--- a/ForHome8/DataScience/model_report_task01.xlsx
+++ b/ForHome8/DataScience/model_report_task01.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="24">
   <si>
     <t xml:space="preserve">Model</t>
   </si>
@@ -59,6 +59,9 @@
     <t xml:space="preserve">Scatter plot test</t>
   </si>
   <si>
+    <t xml:space="preserve">Comments</t>
+  </si>
+  <si>
     <t xml:space="preserve">Base model</t>
   </si>
   <si>
@@ -69,6 +72,9 @@
   </si>
   <si>
     <t xml:space="preserve">{'agglomerative__linkage': 'average', 'agglomerative__distance_threshold': np.float64(1.6000000000000005)}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This is the best model, because it has the best silhouette metric on test data and also it’s simpler than hdbscan. On the diagram we can clearly see the 3 clusters separated.</t>
   </si>
   <si>
     <t xml:space="preserve">dbscan Clustering on ['X', 'Y']</t>
@@ -93,9 +99,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
   </numFmts>
   <fonts count="4">
     <font>
@@ -121,12 +126,18 @@
       <family val="0"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF77BC65"/>
+        <bgColor rgb="FF99CC00"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -163,12 +174,28 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -181,6 +208,66 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF77BC65"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -195,9 +282,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -210,8 +297,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18465840" y="190440"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="18464400" y="190440"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -232,9 +319,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -247,8 +334,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18465840" y="6534000"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="18464400" y="6534000"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -269,9 +356,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -284,8 +371,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25521840" y="6534000"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="25520760" y="6534000"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -306,9 +393,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -321,8 +408,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="35601840" y="6534000"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="35601120" y="6534000"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -343,9 +430,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -358,8 +445,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18465840" y="12877920"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="18464400" y="12877920"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -380,9 +467,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>9524520</xdr:colOff>
+      <xdr:colOff>9524160</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -395,8 +482,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="25521840" y="12877920"/>
-          <a:ext cx="9524520" cy="4762080"/>
+          <a:off x="25520760" y="12877920"/>
+          <a:ext cx="9524160" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -417,9 +504,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -432,8 +519,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="35601840" y="12877920"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="35601120" y="12877920"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -454,9 +541,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -469,8 +556,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18465840" y="19221480"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="18464400" y="19221480"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -491,9 +578,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -506,8 +593,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="35601840" y="19221480"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="35601120" y="19221480"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -528,9 +615,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -543,8 +630,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18465840" y="25565040"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="18464400" y="25565040"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -565,9 +652,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -580,8 +667,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="35601840" y="25565040"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="35601120" y="25565040"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -602,9 +689,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -617,8 +704,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18465840" y="31908600"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="18464400" y="31908600"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -639,9 +726,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -654,8 +741,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="35601840" y="31908600"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="35601120" y="31908600"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -676,9 +763,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -691,8 +778,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18465840" y="38252520"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="18464400" y="38252520"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -713,9 +800,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>6667200</xdr:colOff>
+      <xdr:colOff>6666840</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>4762080</xdr:rowOff>
+      <xdr:rowOff>4761720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -728,8 +815,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="35601840" y="38252520"/>
-          <a:ext cx="6667200" cy="4762080"/>
+          <a:off x="35601120" y="38252520"/>
+          <a:ext cx="6666840" cy="4761720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -750,7 +837,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -767,8 +854,8 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:L8"/>
-  <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M8"/>
+  <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="31.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.26"/>
@@ -777,10 +864,10 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6.98"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="33.8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="20.45"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="29.63"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="100"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="142.86"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="142.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="100"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16.26"/>
   </cols>
@@ -822,10 +909,13 @@
       <c r="L1" s="0" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="0" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" s="0" t="n">
         <v>2</v>
@@ -839,7 +929,7 @@
     </row>
     <row r="3" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B3" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -849,7 +939,7 @@
         <v>2</v>
       </c>
       <c r="D3" s="0" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" s="0" t="n">
         <v>0.716922074968866</v>
@@ -864,36 +954,43 @@
         <v>-172.825527010266</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="1" t="b">
+    <row r="4" s="5" customFormat="true" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3" t="b">
         <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="0" t="s">
-        <v>15</v>
-      </c>
-      <c r="F4" s="0" t="n">
+      <c r="D4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="n">
         <v>0.718077873018322</v>
       </c>
-      <c r="G4" s="0" t="n">
+      <c r="G4" s="2" t="n">
         <v>-171.807787301832</v>
       </c>
-      <c r="H4" s="0" t="n">
+      <c r="H4" s="2" t="n">
         <v>0.72825527010266</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="2" t="n">
         <v>-172.825527010266</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -903,7 +1000,7 @@
         <v>2</v>
       </c>
       <c r="D5" s="0" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F5" s="0" t="n">
         <v>0.708946177860825</v>
@@ -920,7 +1017,7 @@
     </row>
     <row r="6" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="b">
         <f aca="false">FALSE()</f>
@@ -930,7 +1027,7 @@
         <v>2</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F6" s="0" t="n">
         <v>0.718077873018322</v>
@@ -947,7 +1044,7 @@
     </row>
     <row r="7" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B7" s="1" t="b">
         <f aca="false">TRUE()</f>
@@ -957,7 +1054,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F7" s="0" t="n">
         <v>0.708488227426366</v>
@@ -974,7 +1071,7 @@
     </row>
     <row r="8" customFormat="false" ht="499.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B8" s="1" t="b">
         <f aca="false">FALSE()</f>
@@ -984,7 +1081,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="0" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F8" s="0" t="n">
         <v>0.718077873018322</v>
